--- a/CL & CD Graphs of Injection & Suction.xlsx
+++ b/CL & CD Graphs of Injection & Suction.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\casus\OneDrive\Desktop\AERO ORGANISED\MY WORK, PROJECTS ETC\RESEARCH &amp; PATENTS\ANUP SIR\ML_work 1st project\Optimising_conference_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\casus\OneDrive\Desktop\AERO ORGANISED\MY WORK, PROJECTS ETC\RESEARCH &amp; PATENTS\ANUP SIR\Optimising_conference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D2B41D-B6EF-483B-86F7-50E7AC40095A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3BB6A7-753E-4FCC-9FE1-992D9B94FDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PICET 2025" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t>AOA</t>
   </si>
@@ -60,6 +60,33 @@
   </si>
   <si>
     <t>Baseline</t>
+  </si>
+  <si>
+    <t>aoa</t>
+  </si>
+  <si>
+    <t>optimised_cl</t>
+  </si>
+  <si>
+    <t>optimal_suction_loc</t>
+  </si>
+  <si>
+    <t>optimal_suction_slot_size</t>
+  </si>
+  <si>
+    <t>re_values</t>
+  </si>
+  <si>
+    <t>chord_length</t>
+  </si>
+  <si>
+    <t>For graph plotting</t>
+  </si>
+  <si>
+    <t>Optimised Suction # 1</t>
+  </si>
+  <si>
+    <t>optimisation + stabilisation</t>
   </si>
 </sst>
 </file>
@@ -119,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -179,11 +206,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -209,6 +251,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -218,6 +265,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1126,20 +1174,1865 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>CL vs AOA --allowing for</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> variation in Re</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PICET 2025'!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$B$5:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$C$5:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.111</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.1100000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7181-401B-8722-32361BFF81B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PICET 2025'!$G$2:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Injection at 50% C </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$G$5:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$H$5:$H$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.35780000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.51119999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74170000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91910000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0267999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1634</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3983000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.51</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6422000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.7493000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.7793000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6508</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7181-401B-8722-32361BFF81B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PICET 2025'!$L$2:$O$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Suction at 50% C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$L$5:$L$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$M$5:$M$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.6956</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0224</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4434</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7982</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0535999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3268</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6966000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.2844000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.4986000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.5586000000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.3016000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7181-401B-8722-32361BFF81B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PICET 2025'!$U$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Optimised Suction # 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$S$5:$S$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$T$5:$T$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>2.001703419</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.045373605</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0890437899999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1327139750000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1770112780000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2219966489999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.266982021</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.3119673920000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.3569527629999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.401938135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4323373880000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4608614860000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.494622283</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.5461632349999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.6582514000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.769972192</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.8812706540000002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.9906747120000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.1044835119999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.210716788</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.3039491519999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.3754053970000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.4121860439999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.4370633320000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.4587884990000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.4535568620000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.4453679510000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.4371790400000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7181-401B-8722-32361BFF81B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PICET 2025'!$AB$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>optimisation + stabilisation</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$AA$5:$AA$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$AB$5:$AB$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>1.09210219814793</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.16665179402258</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.23299899508085</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2914982123160199</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.34907394615099</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.4113895751030401</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.54207696460594</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6727643541088399</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8034517436117401</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.93413913311464</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.06482652261754</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1955139121204401</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3262013016233398</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.45688869112624</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.5875760806291499</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.7180230085241299</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.8483331049334701</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.9703851010545201</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0827194370778801</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.1814131008577</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.2692480353892299</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.34631146896748</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.3902586096430198</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.4222049832983901</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.4397285287494999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.4548565566187399</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.4690494610669198</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.4832423655151001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA19-49B0-8FBC-D5E84C509E1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="627819712"/>
+        <c:axId val="627820672"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="627819712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>AOA</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="627820672"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="627820672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>CL</a:t>
+                </a:r>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="627819712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>180974</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>33336</xdr:rowOff>
+      <xdr:rowOff>52386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>533399</xdr:colOff>
+      <xdr:colOff>200026</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1166,16 +3059,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>285749</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1195,6 +3088,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>100772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>299357</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10F4F07D-7884-8493-28E9-EC8817675B39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1500,31 +3429,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:R17"/>
+  <dimension ref="B1:AF35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="20" max="20" width="23.140625" customWidth="1"/>
+    <col min="21" max="21" width="22.42578125" customWidth="1"/>
+    <col min="22" max="22" width="19.28515625" customWidth="1"/>
+    <col min="23" max="23" width="22.5703125" customWidth="1"/>
+    <col min="24" max="24" width="18.85546875" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="9" t="s">
+    <row r="1" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:32" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11"/>
-      <c r="G2" s="9" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="11"/>
-      <c r="L2" s="9" t="s">
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="L2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="11"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="16"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="11"/>
+      <c r="AB2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="11"/>
     </row>
-    <row r="4" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -1561,8 +3510,44 @@
       <c r="O4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="S4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="X4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>0</v>
       </c>
@@ -1602,8 +3587,44 @@
         <f>M5/N5</f>
         <v>5.0329209174444687</v>
       </c>
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+      <c r="T5" s="12">
+        <v>2.001703419</v>
+      </c>
+      <c r="U5" s="12">
+        <v>50</v>
+      </c>
+      <c r="V5" s="12">
+        <v>2</v>
+      </c>
+      <c r="W5" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X5" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>1.09210219814793</v>
+      </c>
+      <c r="AC5">
+        <v>50</v>
+      </c>
+      <c r="AD5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
+        <v>1000000</v>
+      </c>
+      <c r="AF5">
+        <v>460</v>
+      </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>2</v>
       </c>
@@ -1643,8 +3664,44 @@
         <f t="shared" ref="O6:O17" si="2">M6/N6</f>
         <v>6.5799974256661091</v>
       </c>
+      <c r="S6" s="12">
+        <v>1</v>
+      </c>
+      <c r="T6" s="12">
+        <v>2.045373605</v>
+      </c>
+      <c r="U6" s="12">
+        <v>50</v>
+      </c>
+      <c r="V6" s="12">
+        <v>2</v>
+      </c>
+      <c r="W6" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X6" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1.16665179402258</v>
+      </c>
+      <c r="AC6">
+        <v>50</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6">
+        <v>1000000</v>
+      </c>
+      <c r="AF6">
+        <v>460</v>
+      </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -1684,8 +3741,44 @@
         <f t="shared" si="2"/>
         <v>7.8652971146772739</v>
       </c>
+      <c r="S7" s="12">
+        <v>2</v>
+      </c>
+      <c r="T7" s="12">
+        <v>2.0890437899999998</v>
+      </c>
+      <c r="U7" s="12">
+        <v>50</v>
+      </c>
+      <c r="V7" s="12">
+        <v>2</v>
+      </c>
+      <c r="W7" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X7" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7">
+        <v>1.23299899508085</v>
+      </c>
+      <c r="AC7">
+        <v>50</v>
+      </c>
+      <c r="AD7">
+        <v>2</v>
+      </c>
+      <c r="AE7">
+        <v>1000000</v>
+      </c>
+      <c r="AF7">
+        <v>460</v>
+      </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -1725,8 +3818,44 @@
         <f t="shared" si="2"/>
         <v>8.2348361687999443</v>
       </c>
+      <c r="S8" s="12">
+        <v>3</v>
+      </c>
+      <c r="T8" s="12">
+        <v>2.1327139750000002</v>
+      </c>
+      <c r="U8" s="12">
+        <v>50</v>
+      </c>
+      <c r="V8" s="12">
+        <v>2</v>
+      </c>
+      <c r="W8" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X8" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
+      <c r="AB8">
+        <v>1.2914982123160199</v>
+      </c>
+      <c r="AC8">
+        <v>50</v>
+      </c>
+      <c r="AD8">
+        <v>2</v>
+      </c>
+      <c r="AE8">
+        <v>1000000</v>
+      </c>
+      <c r="AF8">
+        <v>460</v>
+      </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>8</v>
       </c>
@@ -1766,8 +3895,44 @@
         <f t="shared" si="2"/>
         <v>8.1182795698924739</v>
       </c>
+      <c r="S9" s="12">
+        <v>4</v>
+      </c>
+      <c r="T9" s="12">
+        <v>2.1770112780000002</v>
+      </c>
+      <c r="U9" s="12">
+        <v>50</v>
+      </c>
+      <c r="V9" s="12">
+        <v>2</v>
+      </c>
+      <c r="W9" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X9" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA9">
+        <v>4</v>
+      </c>
+      <c r="AB9">
+        <v>1.34907394615099</v>
+      </c>
+      <c r="AC9">
+        <v>50</v>
+      </c>
+      <c r="AD9">
+        <v>2</v>
+      </c>
+      <c r="AE9">
+        <v>1000000</v>
+      </c>
+      <c r="AF9">
+        <v>460</v>
+      </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>10</v>
       </c>
@@ -1807,8 +3972,44 @@
         <f t="shared" si="2"/>
         <v>7.6635267768921675</v>
       </c>
+      <c r="S10" s="12">
+        <v>5</v>
+      </c>
+      <c r="T10" s="12">
+        <v>2.2219966489999998</v>
+      </c>
+      <c r="U10" s="12">
+        <v>50</v>
+      </c>
+      <c r="V10" s="12">
+        <v>2</v>
+      </c>
+      <c r="W10" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X10" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA10">
+        <v>5</v>
+      </c>
+      <c r="AB10">
+        <v>1.4113895751030401</v>
+      </c>
+      <c r="AC10">
+        <v>50</v>
+      </c>
+      <c r="AD10">
+        <v>2</v>
+      </c>
+      <c r="AE10">
+        <v>2000000</v>
+      </c>
+      <c r="AF10">
+        <v>600</v>
+      </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>13</v>
       </c>
@@ -1848,8 +4049,44 @@
         <f t="shared" si="2"/>
         <v>6.2499420572011299</v>
       </c>
+      <c r="S11" s="12">
+        <v>6</v>
+      </c>
+      <c r="T11" s="12">
+        <v>2.266982021</v>
+      </c>
+      <c r="U11" s="12">
+        <v>50</v>
+      </c>
+      <c r="V11" s="12">
+        <v>2</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X11" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA11">
+        <v>6</v>
+      </c>
+      <c r="AB11">
+        <v>1.54207696460594</v>
+      </c>
+      <c r="AC11">
+        <v>50</v>
+      </c>
+      <c r="AD11">
+        <v>2</v>
+      </c>
+      <c r="AE11">
+        <v>2000000</v>
+      </c>
+      <c r="AF11">
+        <v>600</v>
+      </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>15</v>
       </c>
@@ -1889,8 +4126,44 @@
         <f t="shared" si="2"/>
         <v>5.522134250031999</v>
       </c>
+      <c r="S12" s="12">
+        <v>7</v>
+      </c>
+      <c r="T12" s="12">
+        <v>2.3119673920000001</v>
+      </c>
+      <c r="U12" s="12">
+        <v>50</v>
+      </c>
+      <c r="V12" s="12">
+        <v>2</v>
+      </c>
+      <c r="W12" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X12" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA12">
+        <v>7</v>
+      </c>
+      <c r="AB12">
+        <v>1.6727643541088399</v>
+      </c>
+      <c r="AC12">
+        <v>50</v>
+      </c>
+      <c r="AD12">
+        <v>2</v>
+      </c>
+      <c r="AE12">
+        <v>2000000</v>
+      </c>
+      <c r="AF12">
+        <v>600</v>
+      </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>18</v>
       </c>
@@ -1930,8 +4203,44 @@
         <f t="shared" si="2"/>
         <v>4.8855733973953726</v>
       </c>
+      <c r="S13" s="12">
+        <v>8</v>
+      </c>
+      <c r="T13" s="12">
+        <v>2.3569527629999998</v>
+      </c>
+      <c r="U13" s="12">
+        <v>50</v>
+      </c>
+      <c r="V13" s="12">
+        <v>2</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X13" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA13">
+        <v>8</v>
+      </c>
+      <c r="AB13">
+        <v>1.8034517436117401</v>
+      </c>
+      <c r="AC13">
+        <v>50</v>
+      </c>
+      <c r="AD13">
+        <v>2</v>
+      </c>
+      <c r="AE13">
+        <v>2000000</v>
+      </c>
+      <c r="AF13">
+        <v>600</v>
+      </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>20</v>
       </c>
@@ -1971,8 +4280,44 @@
         <f t="shared" si="2"/>
         <v>4.4777790216052837</v>
       </c>
+      <c r="S14" s="12">
+        <v>9</v>
+      </c>
+      <c r="T14" s="12">
+        <v>2.401938135</v>
+      </c>
+      <c r="U14" s="12">
+        <v>50</v>
+      </c>
+      <c r="V14" s="12">
+        <v>2</v>
+      </c>
+      <c r="W14" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X14" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA14">
+        <v>9</v>
+      </c>
+      <c r="AB14">
+        <v>1.93413913311464</v>
+      </c>
+      <c r="AC14">
+        <v>50</v>
+      </c>
+      <c r="AD14">
+        <v>2</v>
+      </c>
+      <c r="AE14">
+        <v>2000000</v>
+      </c>
+      <c r="AF14">
+        <v>600</v>
+      </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>24</v>
       </c>
@@ -1999,8 +4344,44 @@
         <f t="shared" si="2"/>
         <v>4.0890125173852576</v>
       </c>
+      <c r="S15" s="12">
+        <v>10</v>
+      </c>
+      <c r="T15" s="12">
+        <v>2.4323373880000001</v>
+      </c>
+      <c r="U15" s="12">
+        <v>50</v>
+      </c>
+      <c r="V15" s="12">
+        <v>2</v>
+      </c>
+      <c r="W15" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X15" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA15">
+        <v>10</v>
+      </c>
+      <c r="AB15">
+        <v>2.06482652261754</v>
+      </c>
+      <c r="AC15">
+        <v>50</v>
+      </c>
+      <c r="AD15">
+        <v>2</v>
+      </c>
+      <c r="AE15">
+        <v>2000000</v>
+      </c>
+      <c r="AF15">
+        <v>600</v>
+      </c>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G16" s="4">
         <v>26</v>
       </c>
@@ -2029,8 +4410,44 @@
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="8"/>
+      <c r="S16" s="12">
+        <v>11</v>
+      </c>
+      <c r="T16" s="12">
+        <v>2.4608614860000002</v>
+      </c>
+      <c r="U16" s="12">
+        <v>50</v>
+      </c>
+      <c r="V16" s="12">
+        <v>2</v>
+      </c>
+      <c r="W16" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X16" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA16">
+        <v>11</v>
+      </c>
+      <c r="AB16">
+        <v>2.1955139121204401</v>
+      </c>
+      <c r="AC16">
+        <v>50</v>
+      </c>
+      <c r="AD16">
+        <v>2</v>
+      </c>
+      <c r="AE16">
+        <v>2000000</v>
+      </c>
+      <c r="AF16">
+        <v>600</v>
+      </c>
     </row>
-    <row r="17" spans="7:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:32" x14ac:dyDescent="0.25">
       <c r="G17" s="5">
         <v>28</v>
       </c>
@@ -2059,6 +4476,618 @@
       </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="8"/>
+      <c r="S17" s="12">
+        <v>12</v>
+      </c>
+      <c r="T17" s="12">
+        <v>2.494622283</v>
+      </c>
+      <c r="U17" s="12">
+        <v>50</v>
+      </c>
+      <c r="V17" s="12">
+        <v>2</v>
+      </c>
+      <c r="W17" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="X17" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA17">
+        <v>12</v>
+      </c>
+      <c r="AB17">
+        <v>2.3262013016233398</v>
+      </c>
+      <c r="AC17">
+        <v>50</v>
+      </c>
+      <c r="AD17">
+        <v>2</v>
+      </c>
+      <c r="AE17">
+        <v>2000000</v>
+      </c>
+      <c r="AF17">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S18" s="12">
+        <v>13</v>
+      </c>
+      <c r="T18" s="12">
+        <v>2.5461632349999999</v>
+      </c>
+      <c r="U18" s="12">
+        <v>50</v>
+      </c>
+      <c r="V18" s="12">
+        <v>2</v>
+      </c>
+      <c r="W18" s="12">
+        <v>1674106</v>
+      </c>
+      <c r="X18" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA18">
+        <v>13</v>
+      </c>
+      <c r="AB18">
+        <v>2.45688869112624</v>
+      </c>
+      <c r="AC18">
+        <v>50</v>
+      </c>
+      <c r="AD18">
+        <v>2</v>
+      </c>
+      <c r="AE18">
+        <v>2000000</v>
+      </c>
+      <c r="AF18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S19" s="12">
+        <v>14</v>
+      </c>
+      <c r="T19" s="12">
+        <v>2.6582514000000002</v>
+      </c>
+      <c r="U19" s="12">
+        <v>50</v>
+      </c>
+      <c r="V19" s="12">
+        <v>2</v>
+      </c>
+      <c r="W19" s="12">
+        <v>1697864</v>
+      </c>
+      <c r="X19" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA19">
+        <v>14</v>
+      </c>
+      <c r="AB19">
+        <v>2.5875760806291499</v>
+      </c>
+      <c r="AC19">
+        <v>50</v>
+      </c>
+      <c r="AD19">
+        <v>2</v>
+      </c>
+      <c r="AE19">
+        <v>2000000</v>
+      </c>
+      <c r="AF19">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S20" s="12">
+        <v>15</v>
+      </c>
+      <c r="T20" s="12">
+        <v>2.769972192</v>
+      </c>
+      <c r="U20" s="12">
+        <v>50</v>
+      </c>
+      <c r="V20" s="12">
+        <v>2</v>
+      </c>
+      <c r="W20" s="12">
+        <v>1737737</v>
+      </c>
+      <c r="X20" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA20">
+        <v>15</v>
+      </c>
+      <c r="AB20">
+        <v>2.7180230085241299</v>
+      </c>
+      <c r="AC20">
+        <v>50</v>
+      </c>
+      <c r="AD20">
+        <v>2</v>
+      </c>
+      <c r="AE20">
+        <v>2000000</v>
+      </c>
+      <c r="AF20">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S21" s="12">
+        <v>16</v>
+      </c>
+      <c r="T21" s="12">
+        <v>2.8812706540000002</v>
+      </c>
+      <c r="U21" s="12">
+        <v>50</v>
+      </c>
+      <c r="V21" s="12">
+        <v>2</v>
+      </c>
+      <c r="W21" s="12">
+        <v>1780843</v>
+      </c>
+      <c r="X21" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA21">
+        <v>16</v>
+      </c>
+      <c r="AB21">
+        <v>2.8483331049334701</v>
+      </c>
+      <c r="AC21">
+        <v>50</v>
+      </c>
+      <c r="AD21">
+        <v>2</v>
+      </c>
+      <c r="AE21">
+        <v>2000000</v>
+      </c>
+      <c r="AF21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S22" s="12">
+        <v>17</v>
+      </c>
+      <c r="T22" s="12">
+        <v>2.9906747120000001</v>
+      </c>
+      <c r="U22" s="12">
+        <v>50</v>
+      </c>
+      <c r="V22" s="12">
+        <v>2</v>
+      </c>
+      <c r="W22" s="12">
+        <v>1812961</v>
+      </c>
+      <c r="X22" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA22">
+        <v>17</v>
+      </c>
+      <c r="AB22">
+        <v>2.9703851010545201</v>
+      </c>
+      <c r="AC22">
+        <v>50</v>
+      </c>
+      <c r="AD22">
+        <v>2</v>
+      </c>
+      <c r="AE22">
+        <v>2000000</v>
+      </c>
+      <c r="AF22">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S23" s="12">
+        <v>18</v>
+      </c>
+      <c r="T23" s="12">
+        <v>3.1044835119999998</v>
+      </c>
+      <c r="U23" s="12">
+        <v>50</v>
+      </c>
+      <c r="V23" s="12">
+        <v>2</v>
+      </c>
+      <c r="W23" s="12">
+        <v>1862324</v>
+      </c>
+      <c r="X23" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA23">
+        <v>18</v>
+      </c>
+      <c r="AB23">
+        <v>3.0827194370778801</v>
+      </c>
+      <c r="AC23">
+        <v>50</v>
+      </c>
+      <c r="AD23">
+        <v>2</v>
+      </c>
+      <c r="AE23">
+        <v>2000000</v>
+      </c>
+      <c r="AF23">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S24" s="12">
+        <v>19</v>
+      </c>
+      <c r="T24" s="12">
+        <v>3.210716788</v>
+      </c>
+      <c r="U24" s="12">
+        <v>50</v>
+      </c>
+      <c r="V24" s="12">
+        <v>2</v>
+      </c>
+      <c r="W24" s="12">
+        <v>1922610</v>
+      </c>
+      <c r="X24" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA24">
+        <v>19</v>
+      </c>
+      <c r="AB24">
+        <v>3.1814131008577</v>
+      </c>
+      <c r="AC24">
+        <v>50</v>
+      </c>
+      <c r="AD24">
+        <v>2</v>
+      </c>
+      <c r="AE24">
+        <v>2000000</v>
+      </c>
+      <c r="AF24">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S25" s="12">
+        <v>20</v>
+      </c>
+      <c r="T25" s="12">
+        <v>3.3039491519999999</v>
+      </c>
+      <c r="U25" s="12">
+        <v>50</v>
+      </c>
+      <c r="V25" s="12">
+        <v>2</v>
+      </c>
+      <c r="W25" s="12">
+        <v>1971238</v>
+      </c>
+      <c r="X25" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA25">
+        <v>20</v>
+      </c>
+      <c r="AB25">
+        <v>3.2692480353892299</v>
+      </c>
+      <c r="AC25">
+        <v>50</v>
+      </c>
+      <c r="AD25">
+        <v>2</v>
+      </c>
+      <c r="AE25">
+        <v>2000000</v>
+      </c>
+      <c r="AF25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S26" s="12">
+        <v>21</v>
+      </c>
+      <c r="T26" s="12">
+        <v>3.3754053970000002</v>
+      </c>
+      <c r="U26" s="12">
+        <v>50</v>
+      </c>
+      <c r="V26" s="12">
+        <v>2</v>
+      </c>
+      <c r="W26" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X26" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA26">
+        <v>21</v>
+      </c>
+      <c r="AB26">
+        <v>3.34631146896748</v>
+      </c>
+      <c r="AC26">
+        <v>50</v>
+      </c>
+      <c r="AD26">
+        <v>2</v>
+      </c>
+      <c r="AE26">
+        <v>2000000</v>
+      </c>
+      <c r="AF26">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S27" s="12">
+        <v>22</v>
+      </c>
+      <c r="T27" s="12">
+        <v>3.4121860439999998</v>
+      </c>
+      <c r="U27" s="12">
+        <v>50</v>
+      </c>
+      <c r="V27" s="12">
+        <v>2</v>
+      </c>
+      <c r="W27" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X27" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA27">
+        <v>22</v>
+      </c>
+      <c r="AB27">
+        <v>3.3902586096430198</v>
+      </c>
+      <c r="AC27">
+        <v>50</v>
+      </c>
+      <c r="AD27">
+        <v>2</v>
+      </c>
+      <c r="AE27">
+        <v>2000000</v>
+      </c>
+      <c r="AF27">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S28" s="12">
+        <v>23</v>
+      </c>
+      <c r="T28" s="12">
+        <v>3.4370633320000001</v>
+      </c>
+      <c r="U28" s="12">
+        <v>50</v>
+      </c>
+      <c r="V28" s="12">
+        <v>2</v>
+      </c>
+      <c r="W28" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X28" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA28">
+        <v>23</v>
+      </c>
+      <c r="AB28">
+        <v>3.4222049832983901</v>
+      </c>
+      <c r="AC28">
+        <v>50</v>
+      </c>
+      <c r="AD28">
+        <v>2</v>
+      </c>
+      <c r="AE28">
+        <v>2000000</v>
+      </c>
+      <c r="AF28">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S29" s="12">
+        <v>24</v>
+      </c>
+      <c r="T29" s="12">
+        <v>3.4587884990000002</v>
+      </c>
+      <c r="U29" s="12">
+        <v>50</v>
+      </c>
+      <c r="V29" s="12">
+        <v>2</v>
+      </c>
+      <c r="W29" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X29" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA29">
+        <v>24</v>
+      </c>
+      <c r="AB29">
+        <v>3.4397285287494999</v>
+      </c>
+      <c r="AC29">
+        <v>50</v>
+      </c>
+      <c r="AD29">
+        <v>2</v>
+      </c>
+      <c r="AE29">
+        <v>2000000</v>
+      </c>
+      <c r="AF29">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S30" s="12">
+        <v>25</v>
+      </c>
+      <c r="T30" s="12">
+        <v>3.4535568620000001</v>
+      </c>
+      <c r="U30" s="12">
+        <v>50</v>
+      </c>
+      <c r="V30" s="12">
+        <v>2</v>
+      </c>
+      <c r="W30" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X30" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA30">
+        <v>25</v>
+      </c>
+      <c r="AB30">
+        <v>3.4548565566187399</v>
+      </c>
+      <c r="AC30">
+        <v>50</v>
+      </c>
+      <c r="AD30">
+        <v>2</v>
+      </c>
+      <c r="AE30">
+        <v>2000000</v>
+      </c>
+      <c r="AF30">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="31" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S31" s="12">
+        <v>26</v>
+      </c>
+      <c r="T31" s="12">
+        <v>3.4453679510000002</v>
+      </c>
+      <c r="U31" s="12">
+        <v>50</v>
+      </c>
+      <c r="V31" s="12">
+        <v>2</v>
+      </c>
+      <c r="W31" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X31" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA31">
+        <v>26</v>
+      </c>
+      <c r="AB31">
+        <v>3.4690494610669198</v>
+      </c>
+      <c r="AC31">
+        <v>50</v>
+      </c>
+      <c r="AD31">
+        <v>2</v>
+      </c>
+      <c r="AE31">
+        <v>2000000</v>
+      </c>
+      <c r="AF31">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S32" s="12">
+        <v>27</v>
+      </c>
+      <c r="T32" s="12">
+        <v>3.4371790400000002</v>
+      </c>
+      <c r="U32" s="12">
+        <v>50</v>
+      </c>
+      <c r="V32" s="12">
+        <v>2</v>
+      </c>
+      <c r="W32" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="X32" s="12">
+        <v>600</v>
+      </c>
+      <c r="AA32">
+        <v>27</v>
+      </c>
+      <c r="AB32">
+        <v>3.4832423655151001</v>
+      </c>
+      <c r="AC32">
+        <v>50</v>
+      </c>
+      <c r="AD32">
+        <v>2</v>
+      </c>
+      <c r="AE32">
+        <v>2000000</v>
+      </c>
+      <c r="AF32">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="34" spans="21:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="21:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U35" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/CL & CD Graphs of Injection & Suction.xlsx
+++ b/CL & CD Graphs of Injection & Suction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\casus\OneDrive\Desktop\AERO ORGANISED\MY WORK, PROJECTS ETC\RESEARCH &amp; PATENTS\ANUP SIR\Optimising_conference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3BB6A7-753E-4FCC-9FE1-992D9B94FDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191C750A-457F-4825-AD64-D9D8BED37E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
   <si>
     <t>AOA</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>optimisation + stabilisation</t>
+  </si>
+  <si>
+    <t>Calculated_suction</t>
   </si>
 </sst>
 </file>
@@ -256,6 +259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -265,7 +269,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2125,6 +2128,237 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-BA19-49B0-8FBC-D5E84C509E1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PICET 2025'!$AA$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Calculated_suction</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$Y$36:$Y$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'PICET 2025'!$Z$36:$Z$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>1.16369025971786</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.24913354186229</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3442212751009299</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.43651239789754</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5291609066156</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.63174028144106</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.73326314317009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8344830952098099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.93633394708781</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.0452641518224799</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1523191707020302</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.2580761461679302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3777388265627799</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.49639794926521</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.6158093888716598</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.71094462300836</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.8522603082045999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.9719790976206601</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0902094245203799</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.2060834969884802</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.2979787911071998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.3601181784771201</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.4029657145452501</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.4253480456309799</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.44238874354058</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.4657011033449399</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.4827335625295399</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.49976602171414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5EDF-499C-B978-F313F33FC22C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3429,7 +3663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AF35"/>
+  <dimension ref="B1:AF63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="20" max="20" width="23.140625" customWidth="1"/>
@@ -3437,29 +3671,30 @@
     <col min="22" max="22" width="19.28515625" customWidth="1"/>
     <col min="23" max="23" width="22.5703125" customWidth="1"/>
     <col min="24" max="24" width="18.85546875" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" customWidth="1"/>
     <col min="29" max="29" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:32" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="G2" s="14" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17"/>
+      <c r="G2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16"/>
-      <c r="L2" s="14" t="s">
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="17"/>
+      <c r="L2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
       <c r="T2" s="10"/>
@@ -3470,7 +3705,7 @@
       <c r="AB2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="17"/>
+      <c r="AC2" s="14"/>
       <c r="AD2" s="11"/>
     </row>
     <row r="4" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
@@ -5083,10 +5318,594 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="21:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="21:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="21:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="21:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AA34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB34" s="11"/>
+    </row>
+    <row r="35" spans="21:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="U35" s="13" t="s">
         <v>13</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>1.16369025971786</v>
+      </c>
+      <c r="AA36">
+        <v>370</v>
+      </c>
+      <c r="AB36">
+        <v>1.4030768497089401</v>
+      </c>
+      <c r="AC36">
+        <v>2000000</v>
+      </c>
+      <c r="AD36">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="37" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y37">
+        <v>1</v>
+      </c>
+      <c r="Z37">
+        <v>1.24913354186229</v>
+      </c>
+      <c r="AA37">
+        <v>240</v>
+      </c>
+      <c r="AB37">
+        <v>0.81860430505974402</v>
+      </c>
+      <c r="AC37">
+        <v>2000000</v>
+      </c>
+      <c r="AD37">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="38" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y38">
+        <v>2</v>
+      </c>
+      <c r="Z38">
+        <v>1.3442212751009299</v>
+      </c>
+      <c r="AA38">
+        <v>240</v>
+      </c>
+      <c r="AB38">
+        <v>0.79606329054005198</v>
+      </c>
+      <c r="AC38">
+        <v>2000000</v>
+      </c>
+      <c r="AD38">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="39" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y39">
+        <v>3</v>
+      </c>
+      <c r="Z39">
+        <v>1.43651239789754</v>
+      </c>
+      <c r="AA39">
+        <v>240</v>
+      </c>
+      <c r="AB39">
+        <v>0.77047249571731602</v>
+      </c>
+      <c r="AC39">
+        <v>2000000</v>
+      </c>
+      <c r="AD39">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="40" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y40">
+        <v>4</v>
+      </c>
+      <c r="Z40">
+        <v>1.5291609066156</v>
+      </c>
+      <c r="AA40">
+        <v>240</v>
+      </c>
+      <c r="AB40">
+        <v>0.74402489777622305</v>
+      </c>
+      <c r="AC40">
+        <v>2000000</v>
+      </c>
+      <c r="AD40">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="41" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y41">
+        <v>5</v>
+      </c>
+      <c r="Z41">
+        <v>1.63174028144106</v>
+      </c>
+      <c r="AA41">
+        <v>370</v>
+      </c>
+      <c r="AB41">
+        <v>1.9027261782570299</v>
+      </c>
+      <c r="AC41">
+        <v>2000000</v>
+      </c>
+      <c r="AD41">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y42">
+        <v>6</v>
+      </c>
+      <c r="Z42">
+        <v>1.73326314317009</v>
+      </c>
+      <c r="AA42">
+        <v>370</v>
+      </c>
+      <c r="AB42">
+        <v>1.9178953936183301</v>
+      </c>
+      <c r="AC42">
+        <v>2000000</v>
+      </c>
+      <c r="AD42">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="43" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y43">
+        <v>7</v>
+      </c>
+      <c r="Z43">
+        <v>1.8344830952098099</v>
+      </c>
+      <c r="AA43">
+        <v>370</v>
+      </c>
+      <c r="AB43">
+        <v>2</v>
+      </c>
+      <c r="AC43">
+        <v>2000000</v>
+      </c>
+      <c r="AD43">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y44">
+        <v>8</v>
+      </c>
+      <c r="Z44">
+        <v>1.93633394708781</v>
+      </c>
+      <c r="AA44">
+        <v>370</v>
+      </c>
+      <c r="AB44">
+        <v>2</v>
+      </c>
+      <c r="AC44">
+        <v>2000000</v>
+      </c>
+      <c r="AD44">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y45">
+        <v>9</v>
+      </c>
+      <c r="Z45">
+        <v>2.0452641518224799</v>
+      </c>
+      <c r="AA45">
+        <v>370</v>
+      </c>
+      <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>2000000</v>
+      </c>
+      <c r="AD45">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y46">
+        <v>10</v>
+      </c>
+      <c r="Z46">
+        <v>2.1523191707020302</v>
+      </c>
+      <c r="AA46">
+        <v>370</v>
+      </c>
+      <c r="AB46">
+        <v>2</v>
+      </c>
+      <c r="AC46">
+        <v>2000000</v>
+      </c>
+      <c r="AD46">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y47">
+        <v>11</v>
+      </c>
+      <c r="Z47">
+        <v>2.2580761461679302</v>
+      </c>
+      <c r="AA47">
+        <v>370</v>
+      </c>
+      <c r="AB47">
+        <v>2</v>
+      </c>
+      <c r="AC47">
+        <v>2000000</v>
+      </c>
+      <c r="AD47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="21:30" x14ac:dyDescent="0.25">
+      <c r="Y48">
+        <v>12</v>
+      </c>
+      <c r="Z48">
+        <v>2.3777388265627799</v>
+      </c>
+      <c r="AA48">
+        <v>284</v>
+      </c>
+      <c r="AB48">
+        <v>1.6029833319726401</v>
+      </c>
+      <c r="AC48">
+        <v>2000000</v>
+      </c>
+      <c r="AD48">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y49">
+        <v>13</v>
+      </c>
+      <c r="Z49">
+        <v>2.49639794926521</v>
+      </c>
+      <c r="AA49">
+        <v>287</v>
+      </c>
+      <c r="AB49">
+        <v>1.65365356228209</v>
+      </c>
+      <c r="AC49">
+        <v>2000000</v>
+      </c>
+      <c r="AD49">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="50" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y50">
+        <v>14</v>
+      </c>
+      <c r="Z50">
+        <v>2.6158093888716598</v>
+      </c>
+      <c r="AA50">
+        <v>290</v>
+      </c>
+      <c r="AB50">
+        <v>1.7259047066175299</v>
+      </c>
+      <c r="AC50">
+        <v>2000000</v>
+      </c>
+      <c r="AD50">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y51">
+        <v>15</v>
+      </c>
+      <c r="Z51">
+        <v>2.71094462300836</v>
+      </c>
+      <c r="AA51">
+        <v>323</v>
+      </c>
+      <c r="AB51">
+        <v>2</v>
+      </c>
+      <c r="AC51">
+        <v>2000000</v>
+      </c>
+      <c r="AD51">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="52" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y52">
+        <v>16</v>
+      </c>
+      <c r="Z52">
+        <v>2.8522603082045999</v>
+      </c>
+      <c r="AA52">
+        <v>298</v>
+      </c>
+      <c r="AB52">
+        <v>1.81541996575431</v>
+      </c>
+      <c r="AC52">
+        <v>2000000</v>
+      </c>
+      <c r="AD52">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="53" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y53">
+        <v>17</v>
+      </c>
+      <c r="Z53">
+        <v>2.9719790976206601</v>
+      </c>
+      <c r="AA53">
+        <v>295</v>
+      </c>
+      <c r="AB53">
+        <v>1.85732315256537</v>
+      </c>
+      <c r="AC53">
+        <v>2000000</v>
+      </c>
+      <c r="AD53">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y54">
+        <v>18</v>
+      </c>
+      <c r="Z54">
+        <v>3.0902094245203799</v>
+      </c>
+      <c r="AA54">
+        <v>301</v>
+      </c>
+      <c r="AB54">
+        <v>1.9152752613630399</v>
+      </c>
+      <c r="AC54">
+        <v>2000000</v>
+      </c>
+      <c r="AD54">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="55" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y55">
+        <v>19</v>
+      </c>
+      <c r="Z55">
+        <v>3.2060834969884802</v>
+      </c>
+      <c r="AA55">
+        <v>299</v>
+      </c>
+      <c r="AB55">
+        <v>2</v>
+      </c>
+      <c r="AC55">
+        <v>2000000</v>
+      </c>
+      <c r="AD55">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="56" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y56">
+        <v>20</v>
+      </c>
+      <c r="Z56">
+        <v>3.2979787911071998</v>
+      </c>
+      <c r="AA56">
+        <v>299</v>
+      </c>
+      <c r="AB56">
+        <v>2</v>
+      </c>
+      <c r="AC56">
+        <v>2000000</v>
+      </c>
+      <c r="AD56">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="57" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y57">
+        <v>21</v>
+      </c>
+      <c r="Z57">
+        <v>3.3601181784771201</v>
+      </c>
+      <c r="AA57">
+        <v>295</v>
+      </c>
+      <c r="AB57">
+        <v>2</v>
+      </c>
+      <c r="AC57">
+        <v>2000000</v>
+      </c>
+      <c r="AD57">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="58" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y58">
+        <v>22</v>
+      </c>
+      <c r="Z58">
+        <v>3.4029657145452501</v>
+      </c>
+      <c r="AA58">
+        <v>284</v>
+      </c>
+      <c r="AB58">
+        <v>2</v>
+      </c>
+      <c r="AC58">
+        <v>2000000</v>
+      </c>
+      <c r="AD58">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="59" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y59">
+        <v>23</v>
+      </c>
+      <c r="Z59">
+        <v>3.4253480456309799</v>
+      </c>
+      <c r="AA59">
+        <v>272</v>
+      </c>
+      <c r="AB59">
+        <v>2</v>
+      </c>
+      <c r="AC59">
+        <v>2000000</v>
+      </c>
+      <c r="AD59">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="60" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y60">
+        <v>24</v>
+      </c>
+      <c r="Z60">
+        <v>3.44238874354058</v>
+      </c>
+      <c r="AA60">
+        <v>262</v>
+      </c>
+      <c r="AB60">
+        <v>2</v>
+      </c>
+      <c r="AC60">
+        <v>2000000</v>
+      </c>
+      <c r="AD60">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y61">
+        <v>25</v>
+      </c>
+      <c r="Z61">
+        <v>3.4657011033449399</v>
+      </c>
+      <c r="AA61">
+        <v>240</v>
+      </c>
+      <c r="AB61">
+        <v>2</v>
+      </c>
+      <c r="AC61">
+        <v>2000000</v>
+      </c>
+      <c r="AD61">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="62" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y62">
+        <v>26</v>
+      </c>
+      <c r="Z62">
+        <v>3.4827335625295399</v>
+      </c>
+      <c r="AA62">
+        <v>240</v>
+      </c>
+      <c r="AB62">
+        <v>2</v>
+      </c>
+      <c r="AC62">
+        <v>2000000</v>
+      </c>
+      <c r="AD62">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63" spans="25:30" x14ac:dyDescent="0.25">
+      <c r="Y63">
+        <v>27</v>
+      </c>
+      <c r="Z63">
+        <v>3.49976602171414</v>
+      </c>
+      <c r="AA63">
+        <v>240</v>
+      </c>
+      <c r="AB63">
+        <v>2</v>
+      </c>
+      <c r="AC63">
+        <v>2000000</v>
+      </c>
+      <c r="AD63">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -5096,6 +5915,7 @@
     <mergeCell ref="L2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>